--- a/target/classes/com/mycompany/ocxrst/BASES/TIPOMONEDA.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/TIPOMONEDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B128485-E263-4A21-880F-59CF1711C33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E190922A-1587-47AB-862C-4F3ABA0B70CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{AE138996-7349-4012-AA97-938975CD6540}"/>
+    <workbookView xWindow="2870" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{AE138996-7349-4012-AA97-938975CD6540}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>moneda</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>Leyenda</t>
+  </si>
+  <si>
+    <t>** Selecciona una opción **</t>
   </si>
 </sst>
 </file>
@@ -437,10 +440,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE7502A-D30C-4A1F-B5B3-31EE5262FE39}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="101.1796875" bestFit="1" customWidth="1"/>
   </cols>
@@ -458,28 +461,39 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
